--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101237322</v>
+        <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kohobben, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614212</v>
+        <v>614191</v>
       </c>
       <c r="R2" t="n">
-        <v>7218016</v>
+        <v>7218177</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-05-31</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-05-31</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,34 +759,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Olsson</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Olsson</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101237322</t>
+          <t>https://artportalen.se/Sighting/136934676</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96277348</v>
+        <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>93405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614083</v>
+        <v>614079</v>
       </c>
       <c r="R3" t="n">
-        <v>7218157</v>
+        <v>7218253</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,72 +863,53 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Åsa Stenman</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96277348</t>
+          <t>https://artportalen.se/Sighting/136934678</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56824999</v>
+        <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>80336</v>
+        <v>93423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614350</v>
+        <v>614107</v>
       </c>
       <c r="R4" t="n">
-        <v>7218141</v>
+        <v>7218243</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,76 +965,73 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56824999</t>
+          <t>https://artportalen.se/Sighting/136934663</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96277344</v>
+        <v>101237322</v>
       </c>
       <c r="B5" t="n">
-        <v>80336</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kohobben, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614339</v>
+        <v>614212</v>
       </c>
       <c r="R5" t="n">
-        <v>7218203</v>
+        <v>7218016</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,12 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2017-05-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2017-05-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,59 +1072,56 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jörgen Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson, Åsa Stenman</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96277344</t>
+          <t>https://artportalen.se/Sighting/101237322</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96277345</v>
+        <v>96277348</v>
       </c>
       <c r="B6" t="n">
-        <v>57132</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614203</v>
+        <v>614083</v>
       </c>
       <c r="R6" t="n">
-        <v>7218143</v>
+        <v>7218157</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,6 +1178,21 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1229,63 +1211,51 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96277345</t>
+          <t>https://artportalen.se/Sighting/96277348</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101243000</v>
+        <v>56824999</v>
       </c>
       <c r="B7" t="n">
-        <v>58114</v>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kohobben, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613965</v>
+        <v>614350</v>
       </c>
       <c r="R7" t="n">
-        <v>7218145</v>
+        <v>7218141</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,22 +1282,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-05-31</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-05-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,31 +1298,41 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Olsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Olsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101243000</t>
+          <t>https://artportalen.se/Sighting/56824999</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56825000</v>
+        <v>96277344</v>
       </c>
       <c r="B8" t="n">
-        <v>106244</v>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,21 +1340,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>614351</v>
+        <v>614339</v>
       </c>
       <c r="R8" t="n">
-        <v>7218121</v>
+        <v>7218203</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,12 +1394,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,58 +1410,57 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Carl Jansson, Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56825000</t>
+          <t>https://artportalen.se/Sighting/96277344</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96277347</v>
+        <v>96277345</v>
       </c>
       <c r="B9" t="n">
-        <v>79085</v>
+        <v>57132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>614083</v>
+        <v>614203</v>
       </c>
       <c r="R9" t="n">
-        <v>7218158</v>
+        <v>7218143</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,21 +1517,6 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1580,6 +1534,460 @@
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96277345</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>101243000</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kohobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>613965</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7218145</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-05-31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-05-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101243000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136934677</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kohobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>614354</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7218364</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136934677</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>56825000</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kohobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>614351</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7218121</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56825000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>96277347</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kohobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>614083</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7218158</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96277347</t>
         </is>
@@ -1595,6 +2003,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92364</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92370</v>
+        <v>92374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92374</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92391</v>
+        <v>92394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92394</v>
+        <v>92404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92404</v>
+        <v>92405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92405</v>
+        <v>92408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92408</v>
+        <v>92410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92410</v>
+        <v>92415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92415</v>
+        <v>92427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92427</v>
+        <v>92428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92428</v>
+        <v>92431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92431</v>
+        <v>92432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934676</v>
       </c>
       <c r="B2" t="n">
-        <v>92432</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934678</v>
       </c>
       <c r="B3" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136934663</v>
       </c>
       <c r="B4" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136934677</v>
       </c>
       <c r="B11" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
